--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/106.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/106.xlsx
@@ -426,13 +426,13 @@
         <v>-11.90841978940809</v>
       </c>
       <c r="E2">
-        <v>-12.87297286951392</v>
+        <v>-14.50097738916744</v>
       </c>
       <c r="F2">
-        <v>-3.232532464620199</v>
+        <v>-3.894940600105838</v>
       </c>
       <c r="G2">
-        <v>-10.40238741252964</v>
+        <v>-9.8221414747705</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.36000945112222</v>
       </c>
       <c r="E3">
-        <v>-14.26244454928742</v>
+        <v>-14.81509046023549</v>
       </c>
       <c r="F3">
-        <v>-3.434152948624585</v>
+        <v>-3.829047286682748</v>
       </c>
       <c r="G3">
-        <v>-9.455905753397547</v>
+        <v>-9.918696845968883</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.69497992069337</v>
       </c>
       <c r="E4">
-        <v>-15.24931677588299</v>
+        <v>-15.40640048226106</v>
       </c>
       <c r="F4">
-        <v>-3.035864789317151</v>
+        <v>-3.947126089747401</v>
       </c>
       <c r="G4">
-        <v>-9.913767443660909</v>
+        <v>-9.577889424883072</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.985253558766253</v>
       </c>
       <c r="E5">
-        <v>-15.61735491543437</v>
+        <v>-16.39210436256265</v>
       </c>
       <c r="F5">
-        <v>-3.32159521429959</v>
+        <v>-3.884642336554234</v>
       </c>
       <c r="G5">
-        <v>-9.290937958630124</v>
+        <v>-9.252906411474976</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.235181082001672</v>
       </c>
       <c r="E6">
-        <v>-15.21477357615248</v>
+        <v>-16.95232188205155</v>
       </c>
       <c r="F6">
-        <v>-3.215002553642156</v>
+        <v>-3.661260640878305</v>
       </c>
       <c r="G6">
-        <v>-9.205727826994824</v>
+        <v>-8.813686403143251</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.458889425818365</v>
       </c>
       <c r="E7">
-        <v>-16.47828575140262</v>
+        <v>-17.89895408861496</v>
       </c>
       <c r="F7">
-        <v>-3.403911739850583</v>
+        <v>-3.928173871938751</v>
       </c>
       <c r="G7">
-        <v>-8.843560766089634</v>
+        <v>-8.532134436664855</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.67130555586714</v>
       </c>
       <c r="E8">
-        <v>-17.41543080491996</v>
+        <v>-18.25175391313053</v>
       </c>
       <c r="F8">
-        <v>-3.434569617428193</v>
+        <v>-3.759958131819658</v>
       </c>
       <c r="G8">
-        <v>-8.239647738270245</v>
+        <v>-8.470333172537739</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.883282273526773</v>
       </c>
       <c r="E9">
-        <v>-17.13140944363289</v>
+        <v>-18.93957477320757</v>
       </c>
       <c r="F9">
-        <v>-3.456523838704588</v>
+        <v>-3.89228402584506</v>
       </c>
       <c r="G9">
-        <v>-9.40728708160781</v>
+        <v>-8.163564780686714</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.093699363501946</v>
       </c>
       <c r="E10">
-        <v>-18.29190336368254</v>
+        <v>-19.23435126026286</v>
       </c>
       <c r="F10">
-        <v>-3.185500248591451</v>
+        <v>-3.867299636609224</v>
       </c>
       <c r="G10">
-        <v>-7.909933955286531</v>
+        <v>-7.135269609642612</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.323033403839253</v>
       </c>
       <c r="E11">
-        <v>-19.51381697669822</v>
+        <v>-20.33448967873828</v>
       </c>
       <c r="F11">
-        <v>-3.382695593930082</v>
+        <v>-3.817079034447101</v>
       </c>
       <c r="G11">
-        <v>-8.085151199043537</v>
+        <v>-7.431361492129488</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.58007667319431</v>
       </c>
       <c r="E12">
-        <v>-19.54056667266153</v>
+        <v>-21.48962641403686</v>
       </c>
       <c r="F12">
-        <v>-3.486359147451218</v>
+        <v>-3.870975931142848</v>
       </c>
       <c r="G12">
-        <v>-7.123225844970744</v>
+        <v>-7.127138909798163</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.870925486888997</v>
       </c>
       <c r="E13">
-        <v>-20.64306895456896</v>
+        <v>-21.63667049353992</v>
       </c>
       <c r="F13">
-        <v>-3.258292205745055</v>
+        <v>-3.867716305412832</v>
       </c>
       <c r="G13">
-        <v>-6.083823793642387</v>
+        <v>-6.352981077621752</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.218219455210816</v>
       </c>
       <c r="E14">
-        <v>-19.87034373532211</v>
+        <v>-22.49983839566796</v>
       </c>
       <c r="F14">
-        <v>-3.583797519940315</v>
+        <v>-3.388077496946071</v>
       </c>
       <c r="G14">
-        <v>-5.925109619398648</v>
+        <v>-6.069737422372788</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.631318625772578</v>
       </c>
       <c r="E15">
-        <v>-23.63010022324241</v>
+        <v>-22.73699910792367</v>
       </c>
       <c r="F15">
-        <v>-3.169517727921838</v>
+        <v>-3.176980489853658</v>
       </c>
       <c r="G15">
-        <v>-5.848427453072509</v>
+        <v>-5.574301040238698</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.113946050293307</v>
       </c>
       <c r="E16">
-        <v>-22.58019616693408</v>
+        <v>-24.07940635733545</v>
       </c>
       <c r="F16">
-        <v>-2.642217972567604</v>
+        <v>-3.193956223039229</v>
       </c>
       <c r="G16">
-        <v>-5.212680219347488</v>
+        <v>-5.329552408520379</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.678514465735176</v>
       </c>
       <c r="E17">
-        <v>-23.64942322183314</v>
+        <v>-24.32425188998217</v>
       </c>
       <c r="F17">
-        <v>-2.699865716863227</v>
+        <v>-3.212434614693477</v>
       </c>
       <c r="G17">
-        <v>-4.749412408218496</v>
+        <v>-5.085277184814176</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.321678429064829</v>
       </c>
       <c r="E18">
-        <v>-23.5464955361128</v>
+        <v>-26.19552150485374</v>
       </c>
       <c r="F18">
-        <v>-2.350805775569363</v>
+        <v>-2.539523608907744</v>
       </c>
       <c r="G18">
-        <v>-5.440260361899147</v>
+        <v>-5.068916468759098</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.033711880908958</v>
       </c>
       <c r="E19">
-        <v>-25.50143323675008</v>
+        <v>-26.49993911307136</v>
       </c>
       <c r="F19">
-        <v>-1.951319796997482</v>
+        <v>-2.594840327331889</v>
       </c>
       <c r="G19">
-        <v>-5.050638946836782</v>
+        <v>-5.208657906517274</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.8109053328540616</v>
       </c>
       <c r="E20">
-        <v>-26.56963232804941</v>
+        <v>-26.76598243254799</v>
       </c>
       <c r="F20">
-        <v>-2.096859807832341</v>
+        <v>-2.228807966322066</v>
       </c>
       <c r="G20">
-        <v>-4.182997929722432</v>
+        <v>-4.346366730994387</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.6409316621622483</v>
       </c>
       <c r="E21">
-        <v>-27.17176540295331</v>
+        <v>-27.81650236132136</v>
       </c>
       <c r="F21">
-        <v>-1.743101366629798</v>
+        <v>-2.035148093058583</v>
       </c>
       <c r="G21">
-        <v>-4.545499355727087</v>
+        <v>-4.197554398458607</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.5113508068358436</v>
       </c>
       <c r="E22">
-        <v>-27.47989635985722</v>
+        <v>-28.12279475777816</v>
       </c>
       <c r="F22">
-        <v>-1.5774287144373</v>
+        <v>-1.646776319930063</v>
       </c>
       <c r="G22">
-        <v>-4.180587852569842</v>
+        <v>-4.801457494641379</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.4177381557681159</v>
       </c>
       <c r="E23">
-        <v>-28.0827856899204</v>
+        <v>-27.86266109688155</v>
       </c>
       <c r="F23">
-        <v>-1.535094998317231</v>
+        <v>-1.173479492299135</v>
       </c>
       <c r="G23">
-        <v>-3.774625584725634</v>
+        <v>-3.640382963108188</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.3547137684984247</v>
       </c>
       <c r="E24">
-        <v>-27.83861037142681</v>
+        <v>-29.67828935162087</v>
       </c>
       <c r="F24">
-        <v>-1.559507814045135</v>
+        <v>-1.233724996769938</v>
       </c>
       <c r="G24">
-        <v>-3.658213561382702</v>
+        <v>-4.739073574499352</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.3201205989701066</v>
       </c>
       <c r="E25">
-        <v>-28.61532064780041</v>
+        <v>-29.11015153109255</v>
       </c>
       <c r="F25">
-        <v>-1.211576109153884</v>
+        <v>-1.076341817177254</v>
       </c>
       <c r="G25">
-        <v>-4.309666023146026</v>
+        <v>-4.043868942889021</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.3166456912865712</v>
       </c>
       <c r="E26">
-        <v>-29.20272259675735</v>
+        <v>-29.376090695667</v>
       </c>
       <c r="F26">
-        <v>-1.11933160028034</v>
+        <v>-1.011091316858737</v>
       </c>
       <c r="G26">
-        <v>-3.301201019882158</v>
+        <v>-4.313241412328439</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.3448759953533433</v>
       </c>
       <c r="E27">
-        <v>-28.59728373582785</v>
+        <v>-29.34767452126887</v>
       </c>
       <c r="F27">
-        <v>-0.65225415510963</v>
+        <v>-0.5791126269120449</v>
       </c>
       <c r="G27">
-        <v>-4.515257522225845</v>
+        <v>-4.89420904901514</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.4031407382763535</v>
       </c>
       <c r="E28">
-        <v>-28.53063818385697</v>
+        <v>-29.22507514445921</v>
       </c>
       <c r="F28">
-        <v>-0.9852918140985462</v>
+        <v>-1.151512017144295</v>
       </c>
       <c r="G28">
-        <v>-4.621691561313414</v>
+        <v>-4.667158593749765</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.4879088489183343</v>
       </c>
       <c r="E29">
-        <v>-30.42917374072872</v>
+        <v>-29.07055002589548</v>
       </c>
       <c r="F29">
-        <v>-0.9112771866584103</v>
+        <v>-1.202451642212048</v>
       </c>
       <c r="G29">
-        <v>-4.501439305144928</v>
+        <v>-4.57637681397187</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.5921761544836032</v>
       </c>
       <c r="E30">
-        <v>-28.73377647089305</v>
+        <v>-28.88622301988726</v>
       </c>
       <c r="F30">
-        <v>-0.5860526890126991</v>
+        <v>-0.9593051003053228</v>
       </c>
       <c r="G30">
-        <v>-5.284777280101737</v>
+        <v>-5.151339121050333</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.7065368033849646</v>
       </c>
       <c r="E31">
-        <v>-28.82586751831303</v>
+        <v>-28.19493334872035</v>
       </c>
       <c r="F31">
-        <v>-0.6967184321896991</v>
+        <v>-0.9470941364206553</v>
       </c>
       <c r="G31">
-        <v>-4.893735641003023</v>
+        <v>-6.091067267282313</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.8206174922453577</v>
       </c>
       <c r="E32">
-        <v>-27.88899417323615</v>
+        <v>-29.18836280567903</v>
       </c>
       <c r="F32">
-        <v>-0.8857311643234763</v>
+        <v>-0.7944285091869148</v>
       </c>
       <c r="G32">
-        <v>-4.482450015931668</v>
+        <v>-5.520921803963489</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.9249777781475823</v>
       </c>
       <c r="E33">
-        <v>-27.55333462283961</v>
+        <v>-27.65208252705087</v>
       </c>
       <c r="F33">
-        <v>-0.9852570226676285</v>
+        <v>-1.078687753661982</v>
       </c>
       <c r="G33">
-        <v>-4.615752442615961</v>
+        <v>-5.646434516993878</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.010848583557958</v>
       </c>
       <c r="E34">
-        <v>-28.31371975041555</v>
+        <v>-28.10060976361459</v>
       </c>
       <c r="F34">
-        <v>-1.272772579403101</v>
+        <v>-0.8027328923999799</v>
       </c>
       <c r="G34">
-        <v>-4.819135807821087</v>
+        <v>-5.989999622513903</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.071462739260081</v>
       </c>
       <c r="E35">
-        <v>-27.00476433849844</v>
+        <v>-27.85228183445597</v>
       </c>
       <c r="F35">
-        <v>-1.098430233972903</v>
+        <v>-1.120394395658131</v>
       </c>
       <c r="G35">
-        <v>-5.101909365603475</v>
+        <v>-4.62148299694444</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.103033306686189</v>
       </c>
       <c r="E36">
-        <v>-27.30957592395473</v>
+        <v>-27.25494441352619</v>
       </c>
       <c r="F36">
-        <v>-1.206817138424801</v>
+        <v>-1.156406840127437</v>
       </c>
       <c r="G36">
-        <v>-3.991376932818337</v>
+        <v>-5.848404279253734</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.103706317636153</v>
       </c>
       <c r="E37">
-        <v>-26.16417993624665</v>
+        <v>-26.79027316712513</v>
       </c>
       <c r="F37">
-        <v>-1.270291619031716</v>
+        <v>-1.102438703835049</v>
       </c>
       <c r="G37">
-        <v>-4.773814439388464</v>
+        <v>-5.787953717706642</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.075160242835308</v>
       </c>
       <c r="E38">
-        <v>-24.57948574200248</v>
+        <v>-25.9215624128117</v>
       </c>
       <c r="F38">
-        <v>-0.9039163139171339</v>
+        <v>-1.04797603220319</v>
       </c>
       <c r="G38">
-        <v>-5.969381544895321</v>
+        <v>-5.139196040012286</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.022292355876661</v>
       </c>
       <c r="E39">
-        <v>-25.26925837437683</v>
+        <v>-26.77396613222351</v>
       </c>
       <c r="F39">
-        <v>-1.105265093413401</v>
+        <v>-0.933155198133748</v>
       </c>
       <c r="G39">
-        <v>-4.708964162819681</v>
+        <v>-5.25228427563379</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.9510997585433889</v>
       </c>
       <c r="E40">
-        <v>-23.68255353767325</v>
+        <v>-24.98982435725952</v>
       </c>
       <c r="F40">
-        <v>-1.012496227973885</v>
+        <v>-1.20059692759718</v>
       </c>
       <c r="G40">
-        <v>-4.657418968773229</v>
+        <v>-5.346714276595961</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.8695024563260189</v>
       </c>
       <c r="E41">
-        <v>-23.60705934749138</v>
+        <v>-24.14429938986536</v>
       </c>
       <c r="F41">
-        <v>-1.327806824542891</v>
+        <v>-1.363123440393845</v>
       </c>
       <c r="G41">
-        <v>-4.752593842481736</v>
+        <v>-5.003092891801769</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.787041945203005</v>
       </c>
       <c r="E42">
-        <v>-23.7485832171791</v>
+        <v>-23.66021910386743</v>
       </c>
       <c r="F42">
-        <v>-1.292084308664565</v>
+        <v>-1.345537200432412</v>
       </c>
       <c r="G42">
-        <v>-4.013488066475129</v>
+        <v>-4.866370671575408</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.7127049650711333</v>
       </c>
       <c r="E43">
-        <v>-23.55663931788998</v>
+        <v>-23.73354868347363</v>
       </c>
       <c r="F43">
-        <v>-1.689706460580148</v>
+        <v>-1.315995133746373</v>
       </c>
       <c r="G43">
-        <v>-4.803380921599695</v>
+        <v>-4.588672180104723</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.6556348414727108</v>
       </c>
       <c r="E44">
-        <v>-22.84420620158126</v>
+        <v>-24.01457219496763</v>
       </c>
       <c r="F44">
-        <v>-1.478971450042759</v>
+        <v>-1.602563866540445</v>
       </c>
       <c r="G44">
-        <v>-4.502995261548385</v>
+        <v>-4.912274696022942</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.6235150184151899</v>
       </c>
       <c r="E45">
-        <v>-21.01642805107936</v>
+        <v>-22.57872441288158</v>
       </c>
       <c r="F45">
-        <v>-1.268439389519056</v>
+        <v>-1.535400665888864</v>
       </c>
       <c r="G45">
-        <v>-3.77446667853975</v>
+        <v>-5.364035050857428</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.6212984101762504</v>
       </c>
       <c r="E46">
-        <v>-21.34365558287362</v>
+        <v>-21.65121595205256</v>
       </c>
       <c r="F46">
-        <v>-1.432752690803561</v>
+        <v>-1.675435346964718</v>
       </c>
       <c r="G46">
-        <v>-4.539735695943216</v>
+        <v>-4.265281539101017</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.6523656251390707</v>
       </c>
       <c r="E47">
-        <v>-19.46687481513471</v>
+        <v>-21.68762941154824</v>
       </c>
       <c r="F47">
-        <v>-1.217908977948287</v>
+        <v>-1.932699754517355</v>
       </c>
       <c r="G47">
-        <v>-4.581445259192494</v>
+        <v>-4.893646256273463</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.7196729208178941</v>
       </c>
       <c r="E48">
-        <v>-20.77208970752149</v>
+        <v>-21.8659018478082</v>
       </c>
       <c r="F48">
-        <v>-1.117109090538629</v>
+        <v>-1.751869635588431</v>
       </c>
       <c r="G48">
-        <v>-5.141579632800561</v>
+        <v>-5.018821293658847</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.8230304976453807</v>
       </c>
       <c r="E49">
-        <v>-19.52865225754735</v>
+        <v>-20.19698709396938</v>
       </c>
       <c r="F49">
-        <v>-1.279635603335294</v>
+        <v>-1.76867638182383</v>
       </c>
       <c r="G49">
-        <v>-3.861772385501409</v>
+        <v>-4.532459116847899</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.9613886473959797</v>
       </c>
       <c r="E50">
-        <v>-18.06326976798328</v>
+        <v>-18.92965288665676</v>
       </c>
       <c r="F50">
-        <v>-1.16847449645142</v>
+        <v>-1.885953325242573</v>
       </c>
       <c r="G50">
-        <v>-5.781706718274037</v>
+        <v>-5.167289329458541</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.133687287069763</v>
       </c>
       <c r="E51">
-        <v>-18.11276598888712</v>
+        <v>-19.06130015453375</v>
       </c>
       <c r="F51">
-        <v>-1.449136141296129</v>
+        <v>-1.769661310665759</v>
       </c>
       <c r="G51">
-        <v>-5.112804370973216</v>
+        <v>-5.308308637794876</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.33551639750818</v>
       </c>
       <c r="E52">
-        <v>-16.17754073560522</v>
+        <v>-18.49500089445255</v>
       </c>
       <c r="F52">
-        <v>-1.12435316347611</v>
+        <v>-2.110301725677568</v>
       </c>
       <c r="G52">
-        <v>-4.513857161462734</v>
+        <v>-5.419867401377236</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.562885730238678</v>
       </c>
       <c r="E53">
-        <v>-16.16830717710358</v>
+        <v>-17.96017452872465</v>
       </c>
       <c r="F53">
-        <v>-1.561866176040906</v>
+        <v>-1.833763693763996</v>
       </c>
       <c r="G53">
-        <v>-5.86800270884622</v>
+        <v>-5.633516768299642</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.813826345648255</v>
       </c>
       <c r="E54">
-        <v>-16.71482153424527</v>
+        <v>-17.72731133830223</v>
       </c>
       <c r="F54">
-        <v>-1.349726254388369</v>
+        <v>-1.873647927473986</v>
       </c>
       <c r="G54">
-        <v>-5.306226304650674</v>
+        <v>-5.528022924145226</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.083197464105603</v>
       </c>
       <c r="E55">
-        <v>-16.15766526318555</v>
+        <v>-16.98670205671778</v>
       </c>
       <c r="F55">
-        <v>-1.512417612298192</v>
+        <v>-2.257008077815569</v>
       </c>
       <c r="G55">
-        <v>-5.007668065737041</v>
+        <v>-5.933995123626052</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.367556631279546</v>
       </c>
       <c r="E56">
-        <v>-14.87459460869628</v>
+        <v>-16.65659894392865</v>
       </c>
       <c r="F56">
-        <v>-1.403780540890648</v>
+        <v>-1.999696453320973</v>
       </c>
       <c r="G56">
-        <v>-5.434741682485182</v>
+        <v>-5.912903637995355</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.665464616717657</v>
       </c>
       <c r="E57">
-        <v>-14.87175072701946</v>
+        <v>-16.32573051903222</v>
       </c>
       <c r="F57">
-        <v>-1.62142579230219</v>
+        <v>-2.353502939832878</v>
       </c>
       <c r="G57">
-        <v>-6.097738016543944</v>
+        <v>-5.993174435686063</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.970709964910054</v>
       </c>
       <c r="E58">
-        <v>-14.82449610074942</v>
+        <v>-16.0707276191863</v>
       </c>
       <c r="F58">
-        <v>-1.429075567902534</v>
+        <v>-2.150960482909177</v>
       </c>
       <c r="G58">
-        <v>-5.859077478072344</v>
+        <v>-5.936428374597416</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.278137811425966</v>
       </c>
       <c r="E59">
-        <v>-13.37033516977636</v>
+        <v>-14.94444179179059</v>
       </c>
       <c r="F59">
-        <v>-1.451650236363626</v>
+        <v>-2.550892123143764</v>
       </c>
       <c r="G59">
-        <v>-6.365240027753673</v>
+        <v>-6.329194807922089</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.583207521380136</v>
       </c>
       <c r="E60">
-        <v>-14.39841198136772</v>
+        <v>-14.99166924721658</v>
       </c>
       <c r="F60">
-        <v>-1.852242913785647</v>
+        <v>-2.232343438397214</v>
       </c>
       <c r="G60">
-        <v>-6.799557118141739</v>
+        <v>-6.270343239870465</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.876561374911539</v>
       </c>
       <c r="E61">
-        <v>-13.09054793168645</v>
+        <v>-14.11763300747013</v>
       </c>
       <c r="F61">
-        <v>-1.438737645288787</v>
+        <v>-2.36766802242075</v>
       </c>
       <c r="G61">
-        <v>-7.026203686851323</v>
+        <v>-6.393796793575427</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.151124955537454</v>
       </c>
       <c r="E62">
-        <v>-13.07825765322963</v>
+        <v>-14.27130224444642</v>
       </c>
       <c r="F62">
-        <v>-1.789166049532076</v>
+        <v>-2.433924989133669</v>
       </c>
       <c r="G62">
-        <v>-7.216775240819469</v>
+        <v>-7.141063064336337</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.400361876817094</v>
       </c>
       <c r="E63">
-        <v>-13.49066125263416</v>
+        <v>-14.28212529732475</v>
       </c>
       <c r="F63">
-        <v>-2.151583415196082</v>
+        <v>-2.36795215243991</v>
       </c>
       <c r="G63">
-        <v>-7.270723890927433</v>
+        <v>-7.409002067557251</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.614717353851722</v>
       </c>
       <c r="E64">
-        <v>-13.43490215217772</v>
+        <v>-12.81240905813534</v>
       </c>
       <c r="F64">
-        <v>-1.781549211263334</v>
+        <v>-2.690353573976881</v>
       </c>
       <c r="G64">
-        <v>-6.643021282862841</v>
+        <v>-7.438558618131863</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.789967443397979</v>
       </c>
       <c r="E65">
-        <v>-12.15915856863286</v>
+        <v>-13.70269346262131</v>
       </c>
       <c r="F65">
-        <v>-1.570533384176397</v>
+        <v>-2.389810283097581</v>
       </c>
       <c r="G65">
-        <v>-7.629183140828638</v>
+        <v>-6.883644974839227</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.924866624795546</v>
       </c>
       <c r="E66">
-        <v>-12.43648231686259</v>
+        <v>-14.05055272199451</v>
       </c>
       <c r="F66">
-        <v>-2.036810626436002</v>
+        <v>-2.789703818431639</v>
       </c>
       <c r="G66">
-        <v>-6.664026694309516</v>
+        <v>-7.364193833683215</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.018452111544559</v>
       </c>
       <c r="E67">
-        <v>-11.95837055960676</v>
+        <v>-12.97561978984578</v>
       </c>
       <c r="F67">
-        <v>-2.087570495777348</v>
+        <v>-2.442468770526142</v>
       </c>
       <c r="G67">
-        <v>-7.492791975156204</v>
+        <v>-6.770033673022518</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.07490898417032</v>
       </c>
       <c r="E68">
-        <v>-12.49985378212593</v>
+        <v>-12.88469256024577</v>
       </c>
       <c r="F68">
-        <v>-2.400270906660133</v>
+        <v>-2.736262523807432</v>
       </c>
       <c r="G68">
-        <v>-8.540106230323419</v>
+        <v>-6.894645917666225</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.098689338571289</v>
       </c>
       <c r="E69">
-        <v>-11.99878266165121</v>
+        <v>-13.67459880987772</v>
       </c>
       <c r="F69">
-        <v>-2.099979439471284</v>
+        <v>-2.799399030514004</v>
       </c>
       <c r="G69">
-        <v>-6.628825663590446</v>
+        <v>-7.636688147566166</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.092930848283805</v>
       </c>
       <c r="E70">
-        <v>-11.81199216578282</v>
+        <v>-14.09412117042231</v>
       </c>
       <c r="F70">
-        <v>-1.991743297886695</v>
+        <v>-2.706466148328734</v>
       </c>
       <c r="G70">
-        <v>-7.964746657780244</v>
+        <v>-7.37721089874363</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.062701276042795</v>
       </c>
       <c r="E71">
-        <v>-10.91170889068792</v>
+        <v>-13.08778556254177</v>
       </c>
       <c r="F71">
-        <v>-2.396540768245327</v>
+        <v>-2.797223737714253</v>
       </c>
       <c r="G71">
-        <v>-8.465761309148006</v>
+        <v>-7.452347040302929</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.009867883911949</v>
       </c>
       <c r="E72">
-        <v>-11.94305978898683</v>
+        <v>-12.77048444577232</v>
       </c>
       <c r="F72">
-        <v>-2.116947717350229</v>
+        <v>-3.026205197033106</v>
       </c>
       <c r="G72">
-        <v>-7.538043822132503</v>
+        <v>-7.066615516249207</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.936206239302159</v>
       </c>
       <c r="E73">
-        <v>-12.45365429029968</v>
+        <v>-13.2831620451287</v>
       </c>
       <c r="F73">
-        <v>-2.793031370288685</v>
+        <v>-2.958739642279503</v>
       </c>
       <c r="G73">
-        <v>-7.782411741113805</v>
+        <v>-7.273107483715708</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.845171393409631</v>
       </c>
       <c r="E74">
-        <v>-13.25292995265349</v>
+        <v>-13.55697169752848</v>
       </c>
       <c r="F74">
-        <v>-2.218202378464024</v>
+        <v>-2.942308974844975</v>
       </c>
       <c r="G74">
-        <v>-7.131992169558734</v>
+        <v>-6.63484423538084</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.736932239130658</v>
       </c>
       <c r="E75">
-        <v>-12.8145147985489</v>
+        <v>-13.8638663810283</v>
       </c>
       <c r="F75">
-        <v>-2.575206363150735</v>
+        <v>-3.19169312329478</v>
       </c>
       <c r="G75">
-        <v>-6.132968842172867</v>
+        <v>-7.137666444613044</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.613619713244714</v>
       </c>
       <c r="E76">
-        <v>-12.90665113070896</v>
+        <v>-13.36296281409187</v>
       </c>
       <c r="F76">
-        <v>-2.429403759849189</v>
+        <v>-3.08509880590254</v>
       </c>
       <c r="G76">
-        <v>-7.458080905176946</v>
+        <v>-6.172486824275148</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.479042064444939</v>
       </c>
       <c r="E77">
-        <v>-13.39614294314607</v>
+        <v>-14.57709198028837</v>
       </c>
       <c r="F77">
-        <v>-2.830371687704678</v>
+        <v>-3.550946953847495</v>
       </c>
       <c r="G77">
-        <v>-6.730522312011317</v>
+        <v>-6.401838108690317</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.333351856340816</v>
       </c>
       <c r="E78">
-        <v>-14.15666392494224</v>
+        <v>-14.39230306993137</v>
       </c>
       <c r="F78">
-        <v>-2.598008832647597</v>
+        <v>-3.175318784843643</v>
       </c>
       <c r="G78">
-        <v>-6.495288188172863</v>
+        <v>-5.880771482991189</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.178752338941834</v>
       </c>
       <c r="E79">
-        <v>-15.13746346789353</v>
+        <v>-15.37038552847805</v>
       </c>
       <c r="F79">
-        <v>-2.728487467364756</v>
+        <v>-3.366458764467809</v>
       </c>
       <c r="G79">
-        <v>-5.800676144214061</v>
+        <v>-5.710718690275446</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.017976930701164</v>
       </c>
       <c r="E80">
-        <v>-15.01120055561166</v>
+        <v>-15.56246075351339</v>
       </c>
       <c r="F80">
-        <v>-2.893387252770442</v>
+        <v>-3.627288465322095</v>
       </c>
       <c r="G80">
-        <v>-5.872011779494278</v>
+        <v>-6.150527975713162</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.849854720289054</v>
       </c>
       <c r="E81">
-        <v>-15.37264070853387</v>
+        <v>-16.91679600346137</v>
       </c>
       <c r="F81">
-        <v>-2.977666180698667</v>
+        <v>-3.271063974361418</v>
       </c>
       <c r="G81">
-        <v>-5.741231988510909</v>
+        <v>-5.720541078890463</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.67538923096516</v>
       </c>
       <c r="E82">
-        <v>-16.44530487520476</v>
+        <v>-17.12555865521498</v>
       </c>
       <c r="F82">
-        <v>-3.197810616564455</v>
+        <v>-3.403619326157395</v>
       </c>
       <c r="G82">
-        <v>-5.715456080942142</v>
+        <v>-5.608515528387065</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.497317280023819</v>
       </c>
       <c r="E83">
-        <v>-17.3784331722773</v>
+        <v>-18.08960737281189</v>
       </c>
       <c r="F83">
-        <v>-2.67984904694198</v>
+        <v>-3.689478148087268</v>
       </c>
       <c r="G83">
-        <v>-6.187132677740884</v>
+        <v>-4.94081159857146</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.317257987777988</v>
       </c>
       <c r="E84">
-        <v>-19.66815642782764</v>
+        <v>-18.60141097668478</v>
       </c>
       <c r="F84">
-        <v>-3.371363527859785</v>
+        <v>-3.969554137178197</v>
       </c>
       <c r="G84">
-        <v>-5.654114982644987</v>
+        <v>-4.442372551633251</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.141198466952841</v>
       </c>
       <c r="E85">
-        <v>-18.35628467864959</v>
+        <v>-20.41447611513577</v>
       </c>
       <c r="F85">
-        <v>-3.158718302091541</v>
+        <v>-3.640970609714135</v>
       </c>
       <c r="G85">
-        <v>-5.839194341563482</v>
+        <v>-5.132478943113105</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.976496915012818</v>
       </c>
       <c r="E86">
-        <v>-19.59847679827162</v>
+        <v>-21.38717874656134</v>
       </c>
       <c r="F86">
-        <v>-2.52440507543925</v>
+        <v>-4.033408010055594</v>
       </c>
       <c r="G86">
-        <v>-4.605939985637561</v>
+        <v>-4.965286461743291</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.827893424977348</v>
       </c>
       <c r="E87">
-        <v>-20.38457912973713</v>
+        <v>-21.61546364976201</v>
       </c>
       <c r="F87">
-        <v>-3.388786579442867</v>
+        <v>-3.760655617172815</v>
       </c>
       <c r="G87">
-        <v>-5.016666128512781</v>
+        <v>-4.343893753476551</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.702775322001485</v>
       </c>
       <c r="E88">
-        <v>-22.03497695335858</v>
+        <v>-24.08527525964939</v>
       </c>
       <c r="F88">
-        <v>-3.093312068701297</v>
+        <v>-3.707264024592776</v>
       </c>
       <c r="G88">
-        <v>-4.476017625948864</v>
+        <v>-4.299386779246589</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.611210633342141</v>
       </c>
       <c r="E89">
-        <v>-23.98905877240842</v>
+        <v>-23.83158108879168</v>
       </c>
       <c r="F89">
-        <v>-3.156461000918912</v>
+        <v>-3.890732493699616</v>
       </c>
       <c r="G89">
-        <v>-4.993075180999934</v>
+        <v>-4.618669033236059</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.560046831393326</v>
       </c>
       <c r="E90">
-        <v>-24.37323639332314</v>
+        <v>-26.48461475702941</v>
       </c>
       <c r="F90">
-        <v>-3.420949600591363</v>
+        <v>-3.914123104052466</v>
       </c>
       <c r="G90">
-        <v>-4.142258356316161</v>
+        <v>-3.650261630997373</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.55549211705933</v>
       </c>
       <c r="E91">
-        <v>-25.44645303382296</v>
+        <v>-27.63472941465347</v>
       </c>
       <c r="F91">
-        <v>-3.114510818906339</v>
+        <v>-4.146675655244787</v>
       </c>
       <c r="G91">
-        <v>-4.367732991904843</v>
+        <v>-5.190608812237167</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.605079931876824</v>
       </c>
       <c r="E92">
-        <v>-28.29949581355746</v>
+        <v>-28.83038693537269</v>
       </c>
       <c r="F92">
-        <v>-3.177308523345167</v>
+        <v>-4.113087013796074</v>
       </c>
       <c r="G92">
-        <v>-4.142493405049449</v>
+        <v>-4.680917221010976</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.709427080706672</v>
       </c>
       <c r="E93">
-        <v>-29.09253576720272</v>
+        <v>-30.93498164501546</v>
       </c>
       <c r="F93">
-        <v>-3.310505031510911</v>
+        <v>-4.196059606330083</v>
       </c>
       <c r="G93">
-        <v>-4.875276039076048</v>
+        <v>-4.934372587497577</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.864333158444358</v>
       </c>
       <c r="E94">
-        <v>-31.35042837895315</v>
+        <v>-33.11734836726597</v>
       </c>
       <c r="F94">
-        <v>-4.041936052467415</v>
+        <v>-4.269394972499923</v>
       </c>
       <c r="G94">
-        <v>-4.966809312691357</v>
+        <v>-5.006681523166339</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.065154865024427</v>
       </c>
       <c r="E95">
-        <v>-33.71504353764235</v>
+        <v>-35.69999596400248</v>
       </c>
       <c r="F95">
-        <v>-3.534277716600961</v>
+        <v>-4.411281054721034</v>
       </c>
       <c r="G95">
-        <v>-5.50411085371507</v>
+        <v>-5.266344162539074</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.302037789382553</v>
       </c>
       <c r="E96">
-        <v>-35.84322027568007</v>
+        <v>-36.22235544078725</v>
       </c>
       <c r="F96">
-        <v>-3.686211067050627</v>
+        <v>-4.320009877545779</v>
       </c>
       <c r="G96">
-        <v>-5.139523784020674</v>
+        <v>-5.622191392009795</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.557795866942576</v>
       </c>
       <c r="E97">
-        <v>-37.70719678316228</v>
+        <v>-38.63318594096173</v>
       </c>
       <c r="F97">
-        <v>-3.980869635900439</v>
+        <v>-4.391517036857641</v>
       </c>
       <c r="G97">
-        <v>-5.004311172560221</v>
+        <v>-5.735670272004933</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.826181327462106</v>
       </c>
       <c r="E98">
-        <v>-39.81243227187714</v>
+        <v>-41.19222886693325</v>
       </c>
       <c r="F98">
-        <v>-4.191186320899414</v>
+        <v>-4.30967433746105</v>
       </c>
       <c r="G98">
-        <v>-6.456313135539024</v>
+        <v>-6.36207845676367</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.085699052452218</v>
       </c>
       <c r="E99">
-        <v>-41.6028708899488</v>
+        <v>-43.1449023305667</v>
       </c>
       <c r="F99">
-        <v>-4.455826511806578</v>
+        <v>-4.576936311198073</v>
       </c>
       <c r="G99">
-        <v>-7.148879262354556</v>
+        <v>-6.498294163522522</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.335319438705234</v>
       </c>
       <c r="E100">
-        <v>-43.74738636220619</v>
+        <v>-44.47374680032551</v>
       </c>
       <c r="F100">
-        <v>-4.002191812848498</v>
+        <v>-4.825955977990647</v>
       </c>
       <c r="G100">
-        <v>-6.923540359132985</v>
+        <v>-6.947594783021329</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.550269121604725</v>
       </c>
       <c r="E101">
-        <v>-46.41458283290291</v>
+        <v>-47.28353359633874</v>
       </c>
       <c r="F101">
-        <v>-4.394665661355681</v>
+        <v>-4.751242208462548</v>
       </c>
       <c r="G101">
-        <v>-6.587665650900687</v>
+        <v>-7.039098261726784</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.755736274128506</v>
       </c>
       <c r="E102">
-        <v>-49.00751572622934</v>
+        <v>-48.98964749991357</v>
       </c>
       <c r="F102">
-        <v>-4.450100007951025</v>
+        <v>-4.743058766890292</v>
       </c>
       <c r="G102">
-        <v>-6.614788950503936</v>
+        <v>-7.236777556967746</v>
       </c>
     </row>
   </sheetData>
